--- a/AGENT7/outputs/business_plan.xlsx
+++ b/AGENT7/outputs/business_plan.xlsx
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prix Vente</t>
+          <t>Prix Vente Unitaire</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24000</v>
+        <v>23484</v>
       </c>
     </row>
     <row r="3">
@@ -445,19 +445,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800000</v>
+        <v>782800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
+          <t>ROI (%)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14939948.18</v>
+        <v>14618739.29</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>801</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>
